--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/131.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/131.xlsx
@@ -426,13 +426,13 @@
         <v>-29.51625150229464</v>
       </c>
       <c r="E2">
-        <v>-4.862011780464904</v>
+        <v>-6.006900579084124</v>
       </c>
       <c r="F2">
-        <v>-0.3391330542026595</v>
+        <v>-0.5600853687011095</v>
       </c>
       <c r="G2">
-        <v>-10.6559321637458</v>
+        <v>-10.38362324041305</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-28.97734707658279</v>
       </c>
       <c r="E3">
-        <v>-6.00453671565212</v>
+        <v>-5.717359007981696</v>
       </c>
       <c r="F3">
-        <v>-0.08160267602826234</v>
+        <v>-0.8577302258606301</v>
       </c>
       <c r="G3">
-        <v>-10.33542169736126</v>
+        <v>-10.09374194135785</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-28.15061309784003</v>
       </c>
       <c r="E4">
-        <v>-7.020939121251708</v>
+        <v>-6.557223382866264</v>
       </c>
       <c r="F4">
-        <v>-0.2222951502911142</v>
+        <v>-0.7241976860414799</v>
       </c>
       <c r="G4">
-        <v>-9.934527874737679</v>
+        <v>-9.145734120732151</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-27.09243468713413</v>
       </c>
       <c r="E5">
-        <v>-7.488236882577221</v>
+        <v>-7.417791940913901</v>
       </c>
       <c r="F5">
-        <v>-0.418300929209562</v>
+        <v>-0.4367621890658396</v>
       </c>
       <c r="G5">
-        <v>-9.147352977500855</v>
+        <v>-8.592161248382919</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-25.83588237531293</v>
       </c>
       <c r="E6">
-        <v>-8.486801629060595</v>
+        <v>-9.394307820197735</v>
       </c>
       <c r="F6">
-        <v>-0.05864923434284071</v>
+        <v>-0.8925820500887482</v>
       </c>
       <c r="G6">
-        <v>-9.459431484396871</v>
+        <v>-8.133054792996791</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-24.4243412887152</v>
       </c>
       <c r="E7">
-        <v>-8.726258277638189</v>
+        <v>-9.042155567465258</v>
       </c>
       <c r="F7">
-        <v>-0.01150626850499696</v>
+        <v>-0.547045134193381</v>
       </c>
       <c r="G7">
-        <v>-7.960476054034584</v>
+        <v>-8.625485199781224</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.92582978020974</v>
       </c>
       <c r="E8">
-        <v>-10.12433405802626</v>
+        <v>-9.814500394895461</v>
       </c>
       <c r="F8">
-        <v>-0.1650520999775554</v>
+        <v>-1.168727307593221</v>
       </c>
       <c r="G8">
-        <v>-7.699528922992611</v>
+        <v>-7.635757884269631</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.42376800985759</v>
       </c>
       <c r="E9">
-        <v>-10.61286583397374</v>
+        <v>-10.59149143665753</v>
       </c>
       <c r="F9">
-        <v>-0.3421539732363602</v>
+        <v>-0.3183231584737851</v>
       </c>
       <c r="G9">
-        <v>-6.934984915062245</v>
+        <v>-6.928483003623116</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.96844930034821</v>
       </c>
       <c r="E10">
-        <v>-11.22797298690961</v>
+        <v>-11.92134122764604</v>
       </c>
       <c r="F10">
-        <v>-0.1979456718412327</v>
+        <v>-0.3120754386373765</v>
       </c>
       <c r="G10">
-        <v>-6.132223969426532</v>
+        <v>-5.637469559673532</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.63564311657312</v>
       </c>
       <c r="E11">
-        <v>-11.54664623130338</v>
+        <v>-11.62157436223429</v>
       </c>
       <c r="F11">
-        <v>-0.007322909329363657</v>
+        <v>-0.5262471162588724</v>
       </c>
       <c r="G11">
-        <v>-5.145148400891896</v>
+        <v>-5.72378210297341</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.47280922948218</v>
       </c>
       <c r="E12">
-        <v>-12.02521989290799</v>
+        <v>-12.50675064803961</v>
       </c>
       <c r="F12">
-        <v>-0.3882002227277622</v>
+        <v>-0.4000281303572217</v>
       </c>
       <c r="G12">
-        <v>-4.536666820228312</v>
+        <v>-4.951070979197661</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.47794185083214</v>
       </c>
       <c r="E13">
-        <v>-12.66038365722384</v>
+        <v>-12.64524044014219</v>
       </c>
       <c r="F13">
-        <v>0.02852031480181964</v>
+        <v>-0.3467292996260648</v>
       </c>
       <c r="G13">
-        <v>-3.208555402965654</v>
+        <v>-4.290663491750609</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.66532166125315</v>
       </c>
       <c r="E14">
-        <v>-13.56507766600221</v>
+        <v>-14.01296638773085</v>
       </c>
       <c r="F14">
-        <v>0.06533039139437871</v>
+        <v>0.003744027607727202</v>
       </c>
       <c r="G14">
-        <v>-3.311751728515816</v>
+        <v>-3.664391039358982</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.01728308973855</v>
       </c>
       <c r="E15">
-        <v>-14.04994137800348</v>
+        <v>-15.03583545421339</v>
       </c>
       <c r="F15">
-        <v>0.005581918322594681</v>
+        <v>0.08244629307549055</v>
       </c>
       <c r="G15">
-        <v>-2.057574724781702</v>
+        <v>-2.971401162714423</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.49200322970581</v>
       </c>
       <c r="E16">
-        <v>-15.06771591122739</v>
+        <v>-17.00906366136766</v>
       </c>
       <c r="F16">
-        <v>0.3798916032896658</v>
+        <v>0.4354432556855353</v>
       </c>
       <c r="G16">
-        <v>-0.9386434379634329</v>
+        <v>-1.996948704321028</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.08543012470324</v>
       </c>
       <c r="E17">
-        <v>-16.2950184083122</v>
+        <v>-17.05720134006919</v>
       </c>
       <c r="F17">
-        <v>0.5199189210680332</v>
+        <v>0.1465182832964243</v>
       </c>
       <c r="G17">
-        <v>-0.8017755537333442</v>
+        <v>-1.743327810557463</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.77769861436252</v>
       </c>
       <c r="E18">
-        <v>-17.41198916467413</v>
+        <v>-18.63036151101582</v>
       </c>
       <c r="F18">
-        <v>0.7690904994207409</v>
+        <v>0.6821355424276225</v>
       </c>
       <c r="G18">
-        <v>0.2669281361631019</v>
+        <v>-1.622092322363812</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.54023936657653</v>
       </c>
       <c r="E19">
-        <v>-18.88426852015189</v>
+        <v>-18.79220464357595</v>
       </c>
       <c r="F19">
-        <v>0.6167379903554661</v>
+        <v>1.203792433914222</v>
       </c>
       <c r="G19">
-        <v>0.538902694396387</v>
+        <v>-0.8106776106884444</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.37591790643811</v>
       </c>
       <c r="E20">
-        <v>-19.29321236541456</v>
+        <v>-19.13126960642626</v>
       </c>
       <c r="F20">
-        <v>1.005352499003744</v>
+        <v>1.574268758712972</v>
       </c>
       <c r="G20">
-        <v>0.5827343173363375</v>
+        <v>-0.6009446191389969</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.26739348682205</v>
       </c>
       <c r="E21">
-        <v>-19.78518578160787</v>
+        <v>-20.66794386229309</v>
       </c>
       <c r="F21">
-        <v>1.154344384116456</v>
+        <v>1.447933370426536</v>
       </c>
       <c r="G21">
-        <v>0.7927785001664766</v>
+        <v>-0.1680941004248284</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.1932991512552</v>
       </c>
       <c r="E22">
-        <v>-20.11346844784592</v>
+        <v>-22.01071338962548</v>
       </c>
       <c r="F22">
-        <v>1.137756648358144</v>
+        <v>1.648455878615818</v>
       </c>
       <c r="G22">
-        <v>0.7864950847329398</v>
+        <v>0.4986232868200745</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.1544152787971</v>
       </c>
       <c r="E23">
-        <v>-21.02215204222505</v>
+        <v>-22.02668531745054</v>
       </c>
       <c r="F23">
-        <v>1.414711971438363</v>
+        <v>1.37003087644607</v>
       </c>
       <c r="G23">
-        <v>0.8941970627620494</v>
+        <v>0.05887359120206487</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.13636489433984</v>
       </c>
       <c r="E24">
-        <v>-21.57007475478312</v>
+        <v>-23.30475200816133</v>
       </c>
       <c r="F24">
-        <v>1.400152962957728</v>
+        <v>2.126584613016564</v>
       </c>
       <c r="G24">
-        <v>0.9324967641058777</v>
+        <v>-0.142636005227833</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.13033784289929</v>
       </c>
       <c r="E25">
-        <v>-22.01316782253764</v>
+        <v>-22.69415068686309</v>
       </c>
       <c r="F25">
-        <v>1.35974153911346</v>
+        <v>1.383337173547592</v>
       </c>
       <c r="G25">
-        <v>1.340514880729973</v>
+        <v>-0.5891325926548773</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.14444739396658</v>
       </c>
       <c r="E26">
-        <v>-21.24536505453713</v>
+        <v>-23.00225447292296</v>
       </c>
       <c r="F26">
-        <v>1.073226967127648</v>
+        <v>1.447190612352195</v>
       </c>
       <c r="G26">
-        <v>1.556756404809628</v>
+        <v>0.220345449880017</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.17160181372128</v>
       </c>
       <c r="E27">
-        <v>-22.24275239777851</v>
+        <v>-21.92882499414478</v>
       </c>
       <c r="F27">
-        <v>1.200479321139123</v>
+        <v>1.246392539333628</v>
       </c>
       <c r="G27">
-        <v>1.284874541851442</v>
+        <v>0.4297308341478411</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.21126708037511</v>
       </c>
       <c r="E28">
-        <v>-21.49373826843583</v>
+        <v>-23.61689972151005</v>
       </c>
       <c r="F28">
-        <v>1.20861323472082</v>
+        <v>1.311082174861583</v>
       </c>
       <c r="G28">
-        <v>0.5650526936110901</v>
+        <v>-0.1482242060981228</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.26980093600025</v>
       </c>
       <c r="E29">
-        <v>-22.35343283099998</v>
+        <v>-24.07422578307067</v>
       </c>
       <c r="F29">
-        <v>1.047374551764014</v>
+        <v>1.225023595416603</v>
       </c>
       <c r="G29">
-        <v>0.3595903058073024</v>
+        <v>0.8616378473833172</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.33485275066198</v>
       </c>
       <c r="E30">
-        <v>-21.85192244854652</v>
+        <v>-22.97931775207411</v>
       </c>
       <c r="F30">
-        <v>1.171263114411096</v>
+        <v>1.839552169196403</v>
       </c>
       <c r="G30">
-        <v>0.4776509808287915</v>
+        <v>0.3338375720573118</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.40220229744391</v>
       </c>
       <c r="E31">
-        <v>-21.27644397165177</v>
+        <v>-22.56941839879582</v>
       </c>
       <c r="F31">
-        <v>1.080238033215298</v>
+        <v>1.558479210736041</v>
       </c>
       <c r="G31">
-        <v>0.7617487568268877</v>
+        <v>-0.5302148136924679</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.47012461477259</v>
       </c>
       <c r="E32">
-        <v>-20.66722383492587</v>
+        <v>-21.94788081276906</v>
       </c>
       <c r="F32">
-        <v>0.6781921146981783</v>
+        <v>1.236245735533407</v>
       </c>
       <c r="G32">
-        <v>0.7886204549691519</v>
+        <v>0.5478510989890371</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.52223368648871</v>
       </c>
       <c r="E33">
-        <v>-20.55597281397943</v>
+        <v>-21.66762714185636</v>
       </c>
       <c r="F33">
-        <v>0.9045686219570084</v>
+        <v>1.363529763663191</v>
       </c>
       <c r="G33">
-        <v>0.0868477010089064</v>
+        <v>0.7846842163229585</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.5584921022964</v>
       </c>
       <c r="E34">
-        <v>-20.20772863431558</v>
+        <v>-21.7240292856219</v>
       </c>
       <c r="F34">
-        <v>1.310700501735962</v>
+        <v>1.342244756159685</v>
       </c>
       <c r="G34">
-        <v>-0.1192503115384213</v>
+        <v>0.7244687035091548</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.57862346332622</v>
       </c>
       <c r="E35">
-        <v>-19.22490033500885</v>
+        <v>-20.72450450264889</v>
       </c>
       <c r="F35">
-        <v>1.203057594369458</v>
+        <v>1.048768212969601</v>
       </c>
       <c r="G35">
-        <v>0.8722216614723672</v>
+        <v>-0.5055578705159761</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.56780051433067</v>
       </c>
       <c r="E36">
-        <v>-20.21520514490224</v>
+        <v>-20.93171841629187</v>
       </c>
       <c r="F36">
-        <v>1.523609173889895</v>
+        <v>1.193908525295964</v>
       </c>
       <c r="G36">
-        <v>0.2218815430102389</v>
+        <v>1.373183344111501</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.53213088777071</v>
       </c>
       <c r="E37">
-        <v>-18.15906510714154</v>
+        <v>-20.52983446200716</v>
       </c>
       <c r="F37">
-        <v>1.308448471924207</v>
+        <v>1.132660282722259</v>
       </c>
       <c r="G37">
-        <v>0.5561804315658433</v>
+        <v>0.3096772107117107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.47364825093325</v>
       </c>
       <c r="E38">
-        <v>-17.9721251716309</v>
+        <v>-20.02904863539493</v>
       </c>
       <c r="F38">
-        <v>1.527364140615402</v>
+        <v>1.424565789644227</v>
       </c>
       <c r="G38">
-        <v>-0.01158143896470453</v>
+        <v>0.49410108161343</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.38226129874086</v>
       </c>
       <c r="E39">
-        <v>-18.12761485515826</v>
+        <v>-18.58278083461723</v>
       </c>
       <c r="F39">
-        <v>1.701475185252899</v>
+        <v>1.750261245978012</v>
       </c>
       <c r="G39">
-        <v>-0.2582038394582509</v>
+        <v>0.5374361227224899</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.27362374568638</v>
       </c>
       <c r="E40">
-        <v>-17.53653578530709</v>
+        <v>-19.09825250243634</v>
       </c>
       <c r="F40">
-        <v>1.774175205301147</v>
+        <v>1.468679917918793</v>
       </c>
       <c r="G40">
-        <v>0.00985434340207641</v>
+        <v>0.6451579640248351</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.15528477094287</v>
       </c>
       <c r="E41">
-        <v>-17.68872873975688</v>
+        <v>-18.68294162271888</v>
       </c>
       <c r="F41">
-        <v>1.878088485236791</v>
+        <v>1.378571802448035</v>
       </c>
       <c r="G41">
-        <v>-0.2726676129193267</v>
+        <v>0.3195426364187389</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.02507964507618</v>
       </c>
       <c r="E42">
-        <v>-16.72270107901861</v>
+        <v>-17.30306577936764</v>
       </c>
       <c r="F42">
-        <v>1.864639654602879</v>
+        <v>1.701863193202182</v>
       </c>
       <c r="G42">
-        <v>0.1621626120273259</v>
+        <v>0.6661070961973431</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.90592507124677</v>
       </c>
       <c r="E43">
-        <v>-15.81561603596419</v>
+        <v>-16.27637015234862</v>
       </c>
       <c r="F43">
-        <v>1.797153194428258</v>
+        <v>1.383166133308725</v>
       </c>
       <c r="G43">
-        <v>-0.9527927095982779</v>
+        <v>0.5580012316124425</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.80640454990788</v>
       </c>
       <c r="E44">
-        <v>-14.57373185257468</v>
+        <v>-16.33187112978662</v>
       </c>
       <c r="F44">
-        <v>2.100865228949827</v>
+        <v>1.457472031155228</v>
       </c>
       <c r="G44">
-        <v>-0.1213028497727695</v>
+        <v>1.362496903110734</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.7245384301507</v>
       </c>
       <c r="E45">
-        <v>-15.31838506144797</v>
+        <v>-15.88199893644263</v>
       </c>
       <c r="F45">
-        <v>1.79816993362597</v>
+        <v>1.802578970894554</v>
       </c>
       <c r="G45">
-        <v>0.4256423104068411</v>
+        <v>-0.1383587803910946</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.67651900830445</v>
       </c>
       <c r="E46">
-        <v>-13.8893707466395</v>
+        <v>-14.93624978231071</v>
       </c>
       <c r="F46">
-        <v>1.857646009280299</v>
+        <v>1.273684543374396</v>
       </c>
       <c r="G46">
-        <v>-0.3090207134860636</v>
+        <v>-0.1672068742203038</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.66004377184846</v>
       </c>
       <c r="E47">
-        <v>-13.74538338709161</v>
+        <v>-15.05677964649887</v>
       </c>
       <c r="F47">
-        <v>2.026803221814302</v>
+        <v>1.832064407628205</v>
       </c>
       <c r="G47">
-        <v>-1.358241842883899</v>
+        <v>-0.5065510341777575</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.66831763128811</v>
       </c>
       <c r="E48">
-        <v>-12.91922670302827</v>
+        <v>-13.56045862251439</v>
       </c>
       <c r="F48">
-        <v>2.033785781195474</v>
+        <v>1.718245047191488</v>
       </c>
       <c r="G48">
-        <v>-1.432441100055584</v>
+        <v>-0.1057863228302054</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.71039604120707</v>
       </c>
       <c r="E49">
-        <v>-12.28279043751627</v>
+        <v>-13.26366243605167</v>
       </c>
       <c r="F49">
-        <v>1.864324497125707</v>
+        <v>1.644221048997933</v>
       </c>
       <c r="G49">
-        <v>-0.538418345538782</v>
+        <v>-0.6273064932682133</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.77813310816812</v>
       </c>
       <c r="E50">
-        <v>-11.64977769835406</v>
+        <v>-12.39763706682479</v>
       </c>
       <c r="F50">
-        <v>1.878460656126919</v>
+        <v>1.445496047022675</v>
       </c>
       <c r="G50">
-        <v>-1.0396316296389</v>
+        <v>-0.9662699404886509</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.86498655397751</v>
       </c>
       <c r="E51">
-        <v>-10.4107555105374</v>
+        <v>-13.29713691591637</v>
       </c>
       <c r="F51">
-        <v>1.992390875977718</v>
+        <v>2.009898744872901</v>
       </c>
       <c r="G51">
-        <v>-1.521911903799927</v>
+        <v>-0.9820314478011211</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.97757062503775</v>
       </c>
       <c r="E52">
-        <v>-10.48191142261993</v>
+        <v>-12.46058285553141</v>
       </c>
       <c r="F52">
-        <v>1.669069394811177</v>
+        <v>1.690569786319183</v>
       </c>
       <c r="G52">
-        <v>-1.523500965658777</v>
+        <v>-0.08820070492559688</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.10688036521757</v>
       </c>
       <c r="E53">
-        <v>-10.67437156794592</v>
+        <v>-13.03635115476265</v>
       </c>
       <c r="F53">
-        <v>1.908798126643078</v>
+        <v>1.660813535873991</v>
       </c>
       <c r="G53">
-        <v>-1.466870773664004</v>
+        <v>-1.776562377226206</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.25212267040767</v>
       </c>
       <c r="E54">
-        <v>-10.39664931400351</v>
+        <v>-11.53631225361788</v>
       </c>
       <c r="F54">
-        <v>1.629962944641231</v>
+        <v>1.453018650121013</v>
       </c>
       <c r="G54">
-        <v>-1.692848612174655</v>
+        <v>-0.889985039627225</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.41967728859302</v>
       </c>
       <c r="E55">
-        <v>-9.899422867961302</v>
+        <v>-10.55169520707813</v>
       </c>
       <c r="F55">
-        <v>1.585758545129485</v>
+        <v>1.408602034016598</v>
       </c>
       <c r="G55">
-        <v>-2.198143798924695</v>
+        <v>-1.777946185261621</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.59850164514657</v>
       </c>
       <c r="E56">
-        <v>-8.689156490093346</v>
+        <v>-11.77383071532019</v>
       </c>
       <c r="F56">
-        <v>1.844263694294835</v>
+        <v>1.647150904941495</v>
       </c>
       <c r="G56">
-        <v>-1.954057276314231</v>
+        <v>-2.126530077819181</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.78902303444317</v>
       </c>
       <c r="E57">
-        <v>-9.263566247122284</v>
+        <v>-10.12021314667928</v>
       </c>
       <c r="F57">
-        <v>2.058881185131527</v>
+        <v>1.011883702199016</v>
       </c>
       <c r="G57">
-        <v>-2.170110099298147</v>
+        <v>-2.124325254490026</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.99241362036975</v>
       </c>
       <c r="E58">
-        <v>-7.867569036303736</v>
+        <v>-10.14734323445923</v>
       </c>
       <c r="F58">
-        <v>1.704382869313646</v>
+        <v>1.438660772291638</v>
       </c>
       <c r="G58">
-        <v>-2.700416457597381</v>
+        <v>-1.855647999613855</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.19275042480686</v>
       </c>
       <c r="E59">
-        <v>-8.176623801905215</v>
+        <v>-10.06099882055498</v>
       </c>
       <c r="F59">
-        <v>2.001660306700785</v>
+        <v>1.35584878997331</v>
       </c>
       <c r="G59">
-        <v>-3.016123322404438</v>
+        <v>-2.985742445990546</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.39075421678707</v>
       </c>
       <c r="E60">
-        <v>-7.945793896312233</v>
+        <v>-9.126389712481934</v>
       </c>
       <c r="F60">
-        <v>1.550091904207874</v>
+        <v>1.525742425757992</v>
       </c>
       <c r="G60">
-        <v>-3.171977185302247</v>
+        <v>-2.721759544689062</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.58419039749497</v>
       </c>
       <c r="E61">
-        <v>-8.453870566076818</v>
+        <v>-8.481788608334105</v>
       </c>
       <c r="F61">
-        <v>1.992946756754037</v>
+        <v>1.50324746693509</v>
       </c>
       <c r="G61">
-        <v>-2.84772911300387</v>
+        <v>-2.176840438379485</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.75502145011659</v>
       </c>
       <c r="E62">
-        <v>-7.462270612617239</v>
+        <v>-9.124650778462989</v>
       </c>
       <c r="F62">
-        <v>1.916122766501985</v>
+        <v>1.468063856317687</v>
       </c>
       <c r="G62">
-        <v>-3.521550930976049</v>
+        <v>-2.53989141494366</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.90731025963092</v>
       </c>
       <c r="E63">
-        <v>-6.279374331651642</v>
+        <v>-9.234660997531325</v>
       </c>
       <c r="F63">
-        <v>1.845166406666636</v>
+        <v>1.254540706268564</v>
       </c>
       <c r="G63">
-        <v>-3.381104347018008</v>
+        <v>-3.66462939863781</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.03659985153361</v>
       </c>
       <c r="E64">
-        <v>-7.420395813468311</v>
+        <v>-7.414028779013527</v>
       </c>
       <c r="F64">
-        <v>1.458438091763646</v>
+        <v>1.486559957704105</v>
       </c>
       <c r="G64">
-        <v>-3.032652876282019</v>
+        <v>-3.322530864791683</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.12403798376157</v>
       </c>
       <c r="E65">
-        <v>-6.996616687356512</v>
+        <v>-8.81411973033501</v>
       </c>
       <c r="F65">
-        <v>1.568179409468107</v>
+        <v>1.602674108012294</v>
       </c>
       <c r="G65">
-        <v>-3.846464422927819</v>
+        <v>-2.665556413068855</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.1746905243635</v>
       </c>
       <c r="E66">
-        <v>-6.455319132271658</v>
+        <v>-8.421881425686633</v>
       </c>
       <c r="F66">
-        <v>1.658748383360259</v>
+        <v>1.644133945172583</v>
       </c>
       <c r="G66">
-        <v>-4.102409319659953</v>
+        <v>-2.719342846445394</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.18249492451818</v>
       </c>
       <c r="E67">
-        <v>-6.325650807536025</v>
+        <v>-7.637431987233929</v>
       </c>
       <c r="F67">
-        <v>1.45704443055806</v>
+        <v>0.9869165784421133</v>
       </c>
       <c r="G67">
-        <v>-3.754355114388677</v>
+        <v>-3.102084947877154</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.13252111307708</v>
       </c>
       <c r="E68">
-        <v>-6.147491583126258</v>
+        <v>-7.255808425659532</v>
       </c>
       <c r="F68">
-        <v>1.503090680049462</v>
+        <v>1.086156342221295</v>
       </c>
       <c r="G68">
-        <v>-3.286800146786329</v>
+        <v>-3.398345668186532</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.03606132686763</v>
       </c>
       <c r="E69">
-        <v>-6.849359769575087</v>
+        <v>-7.573449177979554</v>
       </c>
       <c r="F69">
-        <v>1.517160323402226</v>
+        <v>1.064039889112184</v>
       </c>
       <c r="G69">
-        <v>-3.90810347032351</v>
+        <v>-3.849377703002378</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.89165243694468</v>
       </c>
       <c r="E70">
-        <v>-6.597336605626208</v>
+        <v>-7.954438753192877</v>
       </c>
       <c r="F70">
-        <v>1.380736728434441</v>
+        <v>0.6777344236886164</v>
       </c>
       <c r="G70">
-        <v>-4.590929972162506</v>
+        <v>-3.302624554464045</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.69349475798676</v>
       </c>
       <c r="E71">
-        <v>-7.200945963056606</v>
+        <v>-7.664272252677391</v>
       </c>
       <c r="F71">
-        <v>1.236353427535657</v>
+        <v>1.125592203221653</v>
       </c>
       <c r="G71">
-        <v>-3.367835680496609</v>
+        <v>-3.491603736027801</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.45751080053154</v>
       </c>
       <c r="E72">
-        <v>-7.531148702273905</v>
+        <v>-7.8384418914864</v>
       </c>
       <c r="F72">
-        <v>1.056292399773854</v>
+        <v>1.008391630655472</v>
       </c>
       <c r="G72">
-        <v>-3.835725013198424</v>
+        <v>-3.753914811831954</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.18666780412993</v>
       </c>
       <c r="E73">
-        <v>-6.794402209017999</v>
+        <v>-7.73728483910306</v>
       </c>
       <c r="F73">
-        <v>1.19032301510341</v>
+        <v>1.112344503239002</v>
       </c>
       <c r="G73">
-        <v>-3.761442992388257</v>
+        <v>-3.542516615876253</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.88481924533014</v>
       </c>
       <c r="E74">
-        <v>-6.957993332545091</v>
+        <v>-6.932090461221216</v>
       </c>
       <c r="F74">
-        <v>1.201714611753166</v>
+        <v>0.5497701938681513</v>
       </c>
       <c r="G74">
-        <v>-3.827137458069554</v>
+        <v>-4.480500104609037</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.5719192335596</v>
       </c>
       <c r="E75">
-        <v>-7.690668727668101</v>
+        <v>-9.215392340628688</v>
       </c>
       <c r="F75">
-        <v>1.043535648624989</v>
+        <v>0.8857541956815878</v>
       </c>
       <c r="G75">
-        <v>-3.432821689432502</v>
+        <v>-4.332853084103081</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.25193072937964</v>
       </c>
       <c r="E76">
-        <v>-7.995665980558707</v>
+        <v>-8.47668501812746</v>
       </c>
       <c r="F76">
-        <v>0.8244758626954892</v>
+        <v>0.572788567496106</v>
       </c>
       <c r="G76">
-        <v>-3.172973659509568</v>
+        <v>-3.62415797942022</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.93071602978317</v>
       </c>
       <c r="E77">
-        <v>-7.287168108162649</v>
+        <v>-9.882943751047391</v>
       </c>
       <c r="F77">
-        <v>0.8566345950144026</v>
+        <v>0.8460934484412377</v>
       </c>
       <c r="G77">
-        <v>-3.394253833899993</v>
+        <v>-4.090368865533624</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.62415488966789</v>
       </c>
       <c r="E78">
-        <v>-7.942130360840029</v>
+        <v>-9.150617048422971</v>
       </c>
       <c r="F78">
-        <v>0.6977334619887857</v>
+        <v>0.835585559692297</v>
       </c>
       <c r="G78">
-        <v>-3.23546682765439</v>
+        <v>-3.988003486913819</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.33182951988787</v>
       </c>
       <c r="E79">
-        <v>-8.376044211780995</v>
+        <v>-9.126403297903957</v>
       </c>
       <c r="F79">
-        <v>0.5442913632536885</v>
+        <v>0.8242288045726807</v>
       </c>
       <c r="G79">
-        <v>-3.740818293678597</v>
+        <v>-3.254515706687356</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.06142645197327</v>
       </c>
       <c r="E80">
-        <v>-9.341659781384561</v>
+        <v>-10.23691192185694</v>
       </c>
       <c r="F80">
-        <v>0.9641729777904875</v>
+        <v>0.4838595210793923</v>
       </c>
       <c r="G80">
-        <v>-3.19630969501589</v>
+        <v>-2.64432257397997</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.82685532079776</v>
       </c>
       <c r="E81">
-        <v>-10.67508706683913</v>
+        <v>-10.68262244758789</v>
       </c>
       <c r="F81">
-        <v>0.7462297045313725</v>
+        <v>0.2532949035271827</v>
       </c>
       <c r="G81">
-        <v>-3.643200237362108</v>
+        <v>-3.638505883787421</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.62591219003552</v>
       </c>
       <c r="E82">
-        <v>-10.53013967080162</v>
+        <v>-10.61052008443776</v>
       </c>
       <c r="F82">
-        <v>0.5994375869352055</v>
+        <v>0.7116874948097227</v>
       </c>
       <c r="G82">
-        <v>-2.442349501174574</v>
+        <v>-3.330598664270886</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.46944509774309</v>
       </c>
       <c r="E83">
-        <v>-11.60424842068095</v>
+        <v>-11.92177596115078</v>
       </c>
       <c r="F83">
-        <v>0.8274468949928536</v>
+        <v>0.6890214957479533</v>
       </c>
       <c r="G83">
-        <v>-3.370748960571167</v>
+        <v>-3.195144382986067</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.36883550846851</v>
       </c>
       <c r="E84">
-        <v>-12.47784992692266</v>
+        <v>-14.11912740389266</v>
       </c>
       <c r="F84">
-        <v>0.7475093389110475</v>
+        <v>0.5450000716508476</v>
       </c>
       <c r="G84">
-        <v>-3.324593334662648</v>
+        <v>-2.731403163844959</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.31860924498775</v>
       </c>
       <c r="E85">
-        <v>-13.99650085623896</v>
+        <v>-13.71931296222946</v>
       </c>
       <c r="F85">
-        <v>0.7051800472031819</v>
+        <v>0.2422073784131911</v>
       </c>
       <c r="G85">
-        <v>-3.454280645618058</v>
+        <v>-3.071763661282969</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.3296295677564</v>
       </c>
       <c r="E86">
-        <v>-14.28212529732475</v>
+        <v>-14.36791270892606</v>
       </c>
       <c r="F86">
-        <v>0.9783978243229646</v>
+        <v>0.6337564941227783</v>
       </c>
       <c r="G86">
-        <v>-2.331005923052266</v>
+        <v>-2.436681847211341</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.40623706230325</v>
       </c>
       <c r="E87">
-        <v>-16.91766547047084</v>
+        <v>-17.21333406690565</v>
       </c>
       <c r="F87">
-        <v>0.6027158581801652</v>
+        <v>0.659868637256544</v>
       </c>
       <c r="G87">
-        <v>-2.189711839436172</v>
+        <v>-2.427634126252513</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.53432064513384</v>
       </c>
       <c r="E88">
-        <v>-17.59474479020169</v>
+        <v>-18.1248615429616</v>
       </c>
       <c r="F88">
-        <v>0.6186906997492029</v>
+        <v>-0.03281265603836157</v>
       </c>
       <c r="G88">
-        <v>-1.952352345361506</v>
+        <v>-1.619768319395244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.71663256515551</v>
       </c>
       <c r="E89">
-        <v>-19.39646157278944</v>
+        <v>-20.40614825143566</v>
       </c>
       <c r="F89">
-        <v>1.06610029050817</v>
+        <v>0.3962647468964365</v>
       </c>
       <c r="G89">
-        <v>-2.346337059444631</v>
+        <v>-2.825750401168648</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.94109405103243</v>
       </c>
       <c r="E90">
-        <v>-21.46742783445126</v>
+        <v>-21.72961289407335</v>
       </c>
       <c r="F90">
-        <v>0.5014568693587977</v>
+        <v>0.5165495867329357</v>
       </c>
       <c r="G90">
-        <v>-2.13730259300397</v>
+        <v>-1.602692525503683</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.17729733032676</v>
       </c>
       <c r="E91">
-        <v>-22.2477020198689</v>
+        <v>-24.75673927161072</v>
       </c>
       <c r="F91">
-        <v>0.5556457428144317</v>
+        <v>0.1794419455724949</v>
       </c>
       <c r="G91">
-        <v>-1.624406393695763</v>
+        <v>-2.475905190760626</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.40997052323959</v>
       </c>
       <c r="E92">
-        <v>-23.87893986996389</v>
+        <v>-24.96883488023397</v>
       </c>
       <c r="F92">
-        <v>0.3899212128521438</v>
+        <v>0.2959773616541913</v>
       </c>
       <c r="G92">
-        <v>-2.488150898710391</v>
+        <v>-1.451999803101598</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.60879166083504</v>
       </c>
       <c r="E93">
-        <v>-26.63318493227305</v>
+        <v>-27.47311723426774</v>
       </c>
       <c r="F93">
-        <v>0.02038560936716492</v>
+        <v>0.05733742763915582</v>
       </c>
       <c r="G93">
-        <v>-1.835582783100333</v>
+        <v>-1.856475635998673</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.73597600624659</v>
       </c>
       <c r="E94">
-        <v>-29.17774353413104</v>
+        <v>-30.21468256935541</v>
       </c>
       <c r="F94">
-        <v>0.3446098029055058</v>
+        <v>0.3017190874506169</v>
       </c>
       <c r="G94">
-        <v>-1.932651288857303</v>
+        <v>-2.208764029014677</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.78003814320106</v>
       </c>
       <c r="E95">
-        <v>-30.88792174312775</v>
+        <v>-33.4475669561423</v>
       </c>
       <c r="F95">
-        <v>0.1017049488601919</v>
+        <v>0.1964731189871308</v>
       </c>
       <c r="G95">
-        <v>-1.919508423066397</v>
+        <v>-1.947164720501468</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.72615903787742</v>
       </c>
       <c r="E96">
-        <v>-33.96955056958443</v>
+        <v>-34.62979528719176</v>
       </c>
       <c r="F96">
-        <v>-0.1341547894202895</v>
+        <v>0.3958173499753249</v>
       </c>
       <c r="G96">
-        <v>-1.58844393750266</v>
+        <v>-1.297936945340535</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.57042376609246</v>
       </c>
       <c r="E97">
-        <v>-36.15459588421048</v>
+        <v>-36.81958644257784</v>
       </c>
       <c r="F97">
-        <v>-0.02099108323256381</v>
+        <v>-0.2881274296370589</v>
       </c>
       <c r="G97">
-        <v>-2.242988448799663</v>
+        <v>-2.121421906052086</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.33063670379398</v>
       </c>
       <c r="E98">
-        <v>-39.03972743076333</v>
+        <v>-40.60749192492982</v>
       </c>
       <c r="F98">
-        <v>-0.2246121120454022</v>
+        <v>-0.1578501973270945</v>
       </c>
       <c r="G98">
-        <v>-1.940129811230517</v>
+        <v>-2.580508498164978</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.02600489877829</v>
       </c>
       <c r="E99">
-        <v>-41.80583030226158</v>
+        <v>-43.36478691448315</v>
       </c>
       <c r="F99">
-        <v>-0.4037070791987875</v>
+        <v>-0.1828086107014625</v>
       </c>
       <c r="G99">
-        <v>-2.436443487932514</v>
+        <v>-2.478043803178996</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.67095928227642</v>
       </c>
       <c r="E100">
-        <v>-44.76306647620156</v>
+        <v>-45.23593878903051</v>
       </c>
       <c r="F100">
-        <v>-0.2273828055444635</v>
+        <v>-0.2419592347901681</v>
       </c>
       <c r="G100">
-        <v>-2.787576500555312</v>
+        <v>-3.143109228199802</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.31165171348282</v>
       </c>
       <c r="E101">
-        <v>-47.18121725460944</v>
+        <v>-47.60338877244851</v>
       </c>
       <c r="F101">
-        <v>-0.7749190353952591</v>
+        <v>-0.06344786326662223</v>
       </c>
       <c r="G101">
-        <v>-2.892236087233832</v>
+        <v>-2.069065628348512</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.95837377471067</v>
       </c>
       <c r="E102">
-        <v>-49.18726218077879</v>
+        <v>-50.25590732676787</v>
       </c>
       <c r="F102">
-        <v>-0.9056484157440814</v>
+        <v>-0.4205806738748371</v>
       </c>
       <c r="G102">
-        <v>-2.448464078785607</v>
+        <v>-2.070704348390451</v>
       </c>
     </row>
   </sheetData>
